--- a/Variables_info.xlsx
+++ b/Variables_info.xlsx
@@ -1,26 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scelik\Desktop\TRACE3Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://tilburgu-my.sharepoint.com/personal/sifa_celik_tilburguniversity_edu/Documents/TRACE3Code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{706D49A1-BA5F-4117-AA4B-CAC4B8567866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="13_ncr:1_{706D49A1-BA5F-4117-AA4B-CAC4B8567866}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E21C8DD-7625-4EEC-9668-B2765C749026}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
+    <sheet name="first meetings" sheetId="3" r:id="rId2"/>
     <sheet name="Sheet4" sheetId="7" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="8" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet2!$A$1:$E$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -73,7 +75,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="610" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1188" uniqueCount="777">
   <si>
     <t>Explanation</t>
   </si>
@@ -1943,12 +1945,1100 @@
   <si>
     <t>pcb board can be recycled</t>
   </si>
+  <si>
+    <t>question/year</t>
+  </si>
+  <si>
+    <t>9.2</t>
+  </si>
+  <si>
+    <t>9.7</t>
+  </si>
+  <si>
+    <t>9.10</t>
+  </si>
+  <si>
+    <t>20.1</t>
+  </si>
+  <si>
+    <t>Purchased Energy</t>
+  </si>
+  <si>
+    <t>13.6</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Targets</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:Do you have a current emissions reduction target?</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Emission Reduction Activities</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:describe your company’s actions to reduce its GHG emissions</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Engagement with Policy Makers</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Do you engage with policy makers on possible responses to climate change including taxation, regulation and carbon trading</t>
+    </r>
+  </si>
+  <si>
+    <t>External Verification/ Assurance</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>Actions on Engagement with policy makers</t>
+  </si>
+  <si>
+    <t>9.11</t>
+  </si>
+  <si>
+    <t>2.3a</t>
+  </si>
+  <si>
+    <t>9.1</t>
+  </si>
+  <si>
+    <t>Progress target</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>3.1d</t>
+  </si>
+  <si>
+    <t>target</t>
+  </si>
+  <si>
+    <t>actions</t>
+  </si>
+  <si>
+    <t>type of target</t>
+  </si>
+  <si>
+    <t>3.1a/3.1b</t>
+  </si>
+  <si>
+    <t>3.3a</t>
+  </si>
+  <si>
+    <t>Has your organization mapped its value chain?</t>
+  </si>
+  <si>
+    <t>Have you mapped where in your direct operations or elsewhere in your value chain plastics are produced, commercialized, used, and/or disposed of?</t>
+  </si>
+  <si>
+    <t>Which commodities has your organization mapped in your upstream value chain (i.e., supply chain)?</t>
+  </si>
+  <si>
+    <t>Have you identified priority locations across your value chain?</t>
+  </si>
+  <si>
+    <t>Have you identified any environmental risks which have had a substantive effect on your organization in the reporting year, or are anticipated to have a substantive effect on your organization in the future?</t>
+  </si>
+  <si>
+    <t>Provide details of the environmental risks identified which have had a substantive effect on your organization in the reporting year, or are anticipated to have a substantive effect on your organization in the future.</t>
+  </si>
+  <si>
+    <t>Provide the amount and proportion of your financial metrics from the reporting year that are vulnerable to the substantive effects of environmental risks.</t>
+  </si>
+  <si>
+    <t>Within each river basin, how many facilities are exposed to substantive effects of water-related risks, and what percentage of your total number of facilities does this represent?</t>
+  </si>
+  <si>
+    <t>In the reporting year, was your organization subject to any fines, enforcement orders, and/or other penalties for water-related regulatory violations?</t>
+  </si>
+  <si>
+    <t>Provide the total number and financial value of all water-related fines.</t>
+  </si>
+  <si>
+    <t>Provide details for all significant fines, enforcement orders and/or other penalties for water-related regulatory violations in the reporting year, and your plans for resolving them.</t>
+  </si>
+  <si>
+    <t>Are any of your operations or activities regulated by a carbon pricing system (i.e. ETS, Cap &amp; Trade or Carbon Tax)?</t>
+  </si>
+  <si>
+    <t>Select the carbon pricing regulations which impact your operations.</t>
+  </si>
+  <si>
+    <t>Provide details of each Emissions Trading Scheme (ETS) your organization is regulated by.</t>
+  </si>
+  <si>
+    <t>Complete the following table for each of the tax systems you are regulated by.</t>
+  </si>
+  <si>
+    <t>What is your strategy for complying with the systems you are regulated by or anticipate being regulated by?</t>
+  </si>
+  <si>
+    <t>Do you provide monetary incentives for the management of environmental issues, including the attainment of targets?</t>
+  </si>
+  <si>
+    <t>Provide further details on the monetary incentives provided for the management of environmental issues (do not include the names of individuals).</t>
+  </si>
+  <si>
+    <t>Does your organization have an environmental policy that addresses environmental issues?</t>
+  </si>
+  <si>
+    <t>Provide details of your environmental policies.</t>
+  </si>
+  <si>
+    <t>Does the policy framework for the portfolio activities of your organization include environmental requirements that clients/investees need to meet, and/or exclusion policies?</t>
+  </si>
+  <si>
+    <t>Provide details of the policies which include environmental requirements that clients/investees need to meet.</t>
+  </si>
+  <si>
+    <t>Provide details of your exclusion policies related to industries, activities and/or locations exposed or contributing to environmental risks.</t>
+  </si>
+  <si>
+    <t>Does your organization include covenants in financing agreements to reflect and enforce your environmental policies?</t>
+  </si>
+  <si>
+    <t>Provide details of the covenants included in your organization’s financing agreements to reflect and enforce your environmental policies.</t>
+  </si>
+  <si>
+    <t>Does your organization use scenario analysis to identify environmental outcomes?</t>
+  </si>
+  <si>
+    <t>Provide details of the scenarios used in your organization’s scenario analysis.</t>
+  </si>
+  <si>
+    <t>Provide details of the outcomes of your organization’s scenario analysis.</t>
+  </si>
+  <si>
+    <t>Does your organization’s strategy include a climate transition plan?</t>
+  </si>
+  <si>
+    <t>Do you engage with your value chain on environmental issues?</t>
+  </si>
+  <si>
+    <t>Does your organization assess and classify suppliers according to their dependencies and/or impacts on the environment?</t>
+  </si>
+  <si>
+    <t>Does your organization prioritize which suppliers to engage with on environmental issues?</t>
+  </si>
+  <si>
+    <t>Provide details of your environmental engagement strategy with your clients.</t>
+  </si>
+  <si>
+    <t>Provide details of your environmental engagement strategy with your investees.</t>
+  </si>
+  <si>
+    <t>Do your suppliers have to meet environmental requirements as part of your organization’s purchasing process?</t>
+  </si>
+  <si>
+    <t>Provide details of the environmental requirements that suppliers have to meet as part of your organization’s purchasing process, and the compliance measures in place.</t>
+  </si>
+  <si>
+    <t>Provide further details of your organization’s supplier engagement on environmental issues.</t>
+  </si>
+  <si>
+    <t>Provide details of any environmental smallholder engagement activity.</t>
+  </si>
+  <si>
+    <t>Provide details of any environmental engagement activity with other stakeholders in the value chain.</t>
+  </si>
+  <si>
+    <t>Is this your first year of reporting emissions data to CDP?</t>
+  </si>
+  <si>
+    <t>Has your organization undergone any structural changes in the reporting year, or are any previous structural changes being accounted for in this disclosure of emissions data?</t>
+  </si>
+  <si>
+    <t>Has your emissions accounting methodology, boundary, and/or reporting year definition changed in the reporting year?</t>
+  </si>
+  <si>
+    <t>Have your organization’s base year emissions and past years’ emissions been recalculated as a result of any changes or errors reported in 7.1.1 and/or 7.1.2?</t>
+  </si>
+  <si>
+    <t>Select the name of the standard, protocol, or methodology you have used to collect activity data and calculate emissions.</t>
+  </si>
+  <si>
+    <t>Describe your organization’s approach to reporting Scope 2 emissions.</t>
+  </si>
+  <si>
+    <t>Are there any sources (e.g. facilities, specific GHGs, activities, geographies, etc.) of Scope 1, Scope 2 or Scope 3 emissions that are within your selected reporting boundary which are not included in your disclosure?</t>
+  </si>
+  <si>
+    <t>Provide details of the sources of Scope 1, Scope 2, or Scope 3 emissions that are within your selected reporting boundary which are not included in your disclosure.</t>
+  </si>
+  <si>
+    <t>Does your organization break down its Scope 1 emissions by greenhouse gas type?</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 1 emissions by greenhouse gas type and provide the source of each used global warming potential (GWP).</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 1 emissions from electric utilities value chain activities by greenhouse gas type.</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 1 emissions from oil and gas value chain production activities by greenhouse gas type.</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 1 and 2 emissions by country/area.</t>
+  </si>
+  <si>
+    <t>Indicate which gross global Scope 1 emissions breakdowns you are able to provide.</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 1 emissions by business facility.</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 1 emissions by business activity.</t>
+  </si>
+  <si>
+    <t>Do you include emissions pertaining to your business activity(ies) in your direct operations as part of your global gross Scope 1 figure?</t>
+  </si>
+  <si>
+    <t>Select the form(s) in which you are reporting your agricultural/forestry emissions.</t>
+  </si>
+  <si>
+    <t>Report the Scope 1 emissions pertaining to your business activity(ies) and explain any exclusions. If applicable, disaggregate your agricultural/forestry by GHG emissions category.</t>
+  </si>
+  <si>
+    <t>Why do you not include greenhouse gas emissions pertaining your business activity(ies) in your direct operations as part of your global gross Scope 1 figure? Describe any plans to do so in the future.</t>
+  </si>
+  <si>
+    <t>Break down your organization’s total gross global Scope 1 emissions by sector production activity in metric tons CO2e.</t>
+  </si>
+  <si>
+    <t>Indicate which gross global Scope 2 emissions breakdowns you are able to provide.</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 2 emissions by business division.</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 2 emissions by business facility.</t>
+  </si>
+  <si>
+    <t>Break down your total gross global Scope 2 emissions by business activity.</t>
+  </si>
+  <si>
+    <t>Break down your organization’s total gross global Scope 2 emissions by sector production activity in metric tons CO2e.</t>
+  </si>
+  <si>
+    <t>Break down your gross Scope 1 and Scope 2 emissions between your consolidated accounting group and other entities included in your response.</t>
+  </si>
+  <si>
+    <t>Is your organization able to break down your emissions data for any of the subsidiaries included in your CDP response?</t>
+  </si>
+  <si>
+    <t>Break down your gross Scope 1 and Scope 2 emissions by subsidiary.</t>
+  </si>
+  <si>
+    <t>Report your methane emissions as percentages of natural gas and hydrocarbon production or throughput.</t>
+  </si>
+  <si>
+    <t>Disclose the percentage of your organization’s Scope 3, Category 1 emissions by purchased chemical feedstock.</t>
+  </si>
+  <si>
+    <t>Disclose sales of products that are greenhouse gases.</t>
+  </si>
+  <si>
+    <t>Allocate your emissions to your customers listed below according to the goods or services you have sold them in this reporting period.</t>
+  </si>
+  <si>
+    <t>What are the challenges in allocating emissions to different customers, and what would help you to overcome these challenges?</t>
+  </si>
+  <si>
+    <t>Do you plan to develop your capabilities to allocate emissions to your customers in the future?</t>
+  </si>
+  <si>
+    <t>What percentage of your total operational spend in the reporting year was on energy?</t>
+  </si>
+  <si>
+    <t>Select which energy-related activities your organization has undertaken.</t>
+  </si>
+  <si>
+    <t>Report your organization’s energy consumption totals (excluding feedstocks) in MWh.</t>
+  </si>
+  <si>
+    <t>Report your organization’s energy consumption totals (excluding feedstocks) for cement production activities in MWh.</t>
+  </si>
+  <si>
+    <t>Report your organization’s energy consumption totals (excluding feedstocks) for chemical production activities in MWh.</t>
+  </si>
+  <si>
+    <t>Report your organization’s energy consumption totals (excluding feedstocks) for metals and mining production activities in MWh.</t>
+  </si>
+  <si>
+    <t>Report your organization’s energy consumption totals (excluding feedstocks) for steel production activities in MWh.</t>
+  </si>
+  <si>
+    <t>Select the applications of your organization’s consumption of fuel.</t>
+  </si>
+  <si>
+    <t>State how much fuel in MWh your organization has consumed (excluding feedstocks) by fuel type.</t>
+  </si>
+  <si>
+    <t>State how much fuel in MWh your organization has consumed (excluding feedstocks) by fuel for cement production activities.</t>
+  </si>
+  <si>
+    <t>Provide details on the electricity, heat, steam, and cooling your organization has generated and consumed in the reporting year.</t>
+  </si>
+  <si>
+    <t>Provide details on the electricity and heat your organization has generated and consumed for cement production activities.</t>
+  </si>
+  <si>
+    <t>Provide details on electricity, heat, steam, and cooling your organization has generated and consumed for chemical production activities.</t>
+  </si>
+  <si>
+    <t>Provide details on the electricity, heat, steam, and cooling your organization has generated and consumed for metals and mining production activities.</t>
+  </si>
+  <si>
+    <t>Provide details on the electricity, heat, and steam your organization has generated and consumed for steel production activities.</t>
+  </si>
+  <si>
+    <t>Provide details on the electricity, heat, steam, and/or cooling amounts that were accounted for at a zero or near-zero emission factor in the market-based Scope 2 figure reported in 7.7.</t>
+  </si>
+  <si>
+    <t>Provide details on the average emission factor used for all transport movements per mode that directly source energy from the grid.</t>
+  </si>
+  <si>
+    <t>Provide a breakdown by country/area of your electricity/heat/steam/cooling consumption in the reporting year.</t>
+  </si>
+  <si>
+    <t>Provide details of your organization’s renewable electricity purchases in the reporting year by country/area.</t>
+  </si>
+  <si>
+    <t>Provide details of your organization’s low-carbon heat, steam, and cooling purchases in the reporting year by country/area.</t>
+  </si>
+  <si>
+    <t>Provide details of your organization’s renewable electricity generation by country/area in the reporting year.</t>
+  </si>
+  <si>
+    <t>Describe how your organization’s renewable electricity sourcing strategy directly or indirectly contributes to bringing new capacity into the grid in the countries/areas in which you operate.</t>
+  </si>
+  <si>
+    <t>In the reporting year, has your organization faced barriers or challenges to sourcing renewable electricity?</t>
+  </si>
+  <si>
+    <t>Provide details of the country/area-specific challenges to sourcing renewable electricity faced by your organization in the reporting year.</t>
+  </si>
+  <si>
+    <t>Does your organization consume fuels as feedstocks for chemical production activities?</t>
+  </si>
+  <si>
+    <t>Disclose details on your organization’s consumption of feedstocks for chemical production activities.</t>
+  </si>
+  <si>
+    <t>State the percentage, by mass, of primary resource from which your chemical feedstocks derive.</t>
+  </si>
+  <si>
+    <t>Disclose details on your organization’s consumption of feedstocks for steel production activities.</t>
+  </si>
+  <si>
+    <t>Did you have an emissions target that was active in the reporting year?</t>
+  </si>
+  <si>
+    <t>Provide details of your absolute emissions targets and progress made against those targets.</t>
+  </si>
+  <si>
+    <t>Provide details of your emissions intensity targets and progress made against those targets.</t>
+  </si>
+  <si>
+    <t>Explain why you did not have an emissions target, and forecast how your emissions will change over the next five years.</t>
+  </si>
+  <si>
+    <t>Provide details of the climate-related targets for your portfolio.</t>
+  </si>
+  <si>
+    <t>Did you have any other climate-related targets that were active in the reporting year?</t>
+  </si>
+  <si>
+    <t>Provide details of your targets to increase or maintain low-carbon energy consumption or production.</t>
+  </si>
+  <si>
+    <t>Provide details of any other climate-related targets, including methane reduction targets.</t>
+  </si>
+  <si>
+    <t>Provide details of your net-zero target(s).</t>
+  </si>
+  <si>
+    <t>Indicate which targets reported in 7.53.1/7.53.2 incorporate methane emissions, or if you do not have a methane-specific emissions reduction target for your oil and gas activities, please explain why not and forecast how your methane emissions will change over the next five years.</t>
+  </si>
+  <si>
+    <t>Did you have emissions reduction initiatives that were active within the reporting year? Note that this can include those in the planning and/or implementation phases.</t>
+  </si>
+  <si>
+    <t>Identify the total number of initiatives at each stage of development, and for those in the implementation stages, the estimated CO2e savings.</t>
+  </si>
+  <si>
+    <t>Provide details on the initiatives implemented in the reporting year in the table below.</t>
+  </si>
+  <si>
+    <t>What methods do you use to drive investment in emissions reduction activities?</t>
+  </si>
+  <si>
+    <t>Why did you not have any emissions reduction initiatives active during the reporting year?</t>
+  </si>
+  <si>
+    <t>Describe any planned climate-related projects within your public authority for which you hope to attract financing.</t>
+  </si>
+  <si>
+    <t>Describe your organization’s efforts to reduce methane emissions from your activities.</t>
+  </si>
+  <si>
+    <t>Does your organization conduct leak detection and repair (LDAR) or use other methods to find and fix fugitive methane emissions from oil and gas production activities?</t>
+  </si>
+  <si>
+    <t>Describe the protocol through which methane leak detection and repair or other leak detection methods, are conducted for oil and gas production activities, including predominant frequency of inspections, estimates of assets covered, and methodologies employed.</t>
+  </si>
+  <si>
+    <t>Explain why you do not conduct LDAR or use other methods to find and fix fugitive methane emissions, and whether you have a plan to do so from your oil and gas production activities.</t>
+  </si>
+  <si>
+    <t>If flaring is relevant to your oil and gas production activities, describe your organization’s efforts to reduce flaring, including any flaring reduction targets.</t>
+  </si>
+  <si>
+    <t>Do you classify any of your existing goods and/or services as low-carbon products?</t>
+  </si>
+  <si>
+    <t>Provide details of your products and/or services that you classify as low-carbon products.</t>
+  </si>
+  <si>
+    <t>Provide tracking metrics for the implementation of low-carbon transport technology over the reporting year.</t>
+  </si>
+  <si>
+    <t>Does your organization manage net zero carbon buildings?</t>
+  </si>
+  <si>
+    <t>Provide details of the net zero carbon buildings under your organization’s management in the reporting year.</t>
+  </si>
+  <si>
+    <t>Did your organization complete new construction or major renovations projects designed as net zero carbon in the last three years?</t>
+  </si>
+  <si>
+    <t>Provide details of new construction or major renovations projects completed in the last 3 years that were designed as net zero carbon.</t>
+  </si>
+  <si>
+    <t>Explain your organization’s plan to manage, develop or construct net zero carbon buildings, or explain why you do not plan to do so.</t>
+  </si>
+  <si>
+    <t>Did your organization have a no-deforestation or no-conversion target, or any other targets for sustainable production/ sourcing of your disclosed commodities, active in the reporting year?</t>
+  </si>
+  <si>
+    <t>Provide details on your no-deforestation or no-conversion target that was active during the reporting year.</t>
+  </si>
+  <si>
+    <t>Provide details of other targets related to your commodities, including any which contribute to your no-deforestation or no-conversion target, and progress made against them.</t>
+  </si>
+  <si>
+    <t>Does your organization calculate the GHG emission reductions and/or removals from land use management and land use change that have occurred in your direct operations and/or upstream value chain?</t>
+  </si>
+  <si>
+    <t>Provide details on the actions your organization has taken in its direct operations and/or upstream value chain that have resulted in reduced GHG emissions and/or enhanced removals.</t>
+  </si>
+  <si>
+    <t>Is your organization supporting or implementing project(s) focused on ecosystem restoration and long-term protection?</t>
+  </si>
+  <si>
+    <t>Provide details on your project(s), including the extent, duration, and monitoring frequency. Please specify any measured outcome(s).</t>
+  </si>
+  <si>
+    <t>Do you have plastics-related targets, and if so what type?</t>
+  </si>
+  <si>
+    <t>Indicate whether your organization engages in the following activities.</t>
+  </si>
+  <si>
+    <t>Provide the total weight of plastic durable goods and durable components produced, sold and/or used, and indicate the raw material content.</t>
+  </si>
+  <si>
+    <t>Provide the total weight of waste generated by the plastic you produce, commercialize, use and/or process and indicate the end-of-life management pathways.</t>
+  </si>
+  <si>
+    <t>Does your organization measure the impact of your portfolio on the environment?</t>
+  </si>
+  <si>
+    <t>Provide details of your organization's financed emissions in the reporting year and in the base year.</t>
+  </si>
+  <si>
+    <t>Disclose or restate your financed emissions for previous years.</t>
+  </si>
+  <si>
+    <t>Provide details of the other metrics used to track the impact of your portfolio on the environment.</t>
+  </si>
+  <si>
+    <t>Are you able to provide a breakdown of your organization's financed emissions and other portfolio carbon footprinting metrics?</t>
+  </si>
+  <si>
+    <t>Break down your organization’s financed emissions and other portfolio carbon footprinting metrics by asset class, by industry, and/or by scope.</t>
+  </si>
+  <si>
+    <t>Do any of your existing products and services enable clients to mitigate and/or adapt to the effects of environmental issues?</t>
+  </si>
+  <si>
+    <t>Provide details of your existing products and services that enable clients to mitigate and/or adapt to the effects of environmental issues, including any taxonomy or methodology used to classify the products and services.</t>
+  </si>
+  <si>
+    <t>Question text</t>
+  </si>
+  <si>
+    <t>2025_question_number</t>
+  </si>
+  <si>
+    <t>1.24.1</t>
+  </si>
+  <si>
+    <t>1.24.2</t>
+  </si>
+  <si>
+    <t>3.1.1</t>
+  </si>
+  <si>
+    <t>3.1.2</t>
+  </si>
+  <si>
+    <t>3.3.1</t>
+  </si>
+  <si>
+    <t>3.3.2</t>
+  </si>
+  <si>
+    <t>3.5.1</t>
+  </si>
+  <si>
+    <t>3.5.2</t>
+  </si>
+  <si>
+    <t>3.5.3</t>
+  </si>
+  <si>
+    <t>3.5.4</t>
+  </si>
+  <si>
+    <t>4.5.1</t>
+  </si>
+  <si>
+    <t>4.6.1</t>
+  </si>
+  <si>
+    <t>4.7.1</t>
+  </si>
+  <si>
+    <t>4.7.2</t>
+  </si>
+  <si>
+    <t>4.8.1</t>
+  </si>
+  <si>
+    <t>5.1.1</t>
+  </si>
+  <si>
+    <t>5.1.2</t>
+  </si>
+  <si>
+    <t>5.11</t>
+  </si>
+  <si>
+    <t>5.11.1</t>
+  </si>
+  <si>
+    <t>5.11.2</t>
+  </si>
+  <si>
+    <t>5.11.3</t>
+  </si>
+  <si>
+    <t>5.11.4</t>
+  </si>
+  <si>
+    <t>5.11.5</t>
+  </si>
+  <si>
+    <t>5.11.6</t>
+  </si>
+  <si>
+    <t>5.11.7</t>
+  </si>
+  <si>
+    <t>5.11.8</t>
+  </si>
+  <si>
+    <t>5.11.9</t>
+  </si>
+  <si>
+    <t>7.1.1</t>
+  </si>
+  <si>
+    <t>7.1.2</t>
+  </si>
+  <si>
+    <t>7.1.3</t>
+  </si>
+  <si>
+    <t>7.4.1</t>
+  </si>
+  <si>
+    <t>7.15.1</t>
+  </si>
+  <si>
+    <t>7.15.3</t>
+  </si>
+  <si>
+    <t>7.15.4</t>
+  </si>
+  <si>
+    <t>7.16</t>
+  </si>
+  <si>
+    <t>7.17.1</t>
+  </si>
+  <si>
+    <t>7.17.2</t>
+  </si>
+  <si>
+    <t>7.17.3</t>
+  </si>
+  <si>
+    <t>7.18.1</t>
+  </si>
+  <si>
+    <t>7.18.2</t>
+  </si>
+  <si>
+    <t>7.18.3</t>
+  </si>
+  <si>
+    <t>7.20</t>
+  </si>
+  <si>
+    <t>7.20.1</t>
+  </si>
+  <si>
+    <t>7.20.2</t>
+  </si>
+  <si>
+    <t>7.20.3</t>
+  </si>
+  <si>
+    <t>7.23.1</t>
+  </si>
+  <si>
+    <t>7.25.1</t>
+  </si>
+  <si>
+    <t>7.30</t>
+  </si>
+  <si>
+    <t>7.30.1</t>
+  </si>
+  <si>
+    <t>7.30.2</t>
+  </si>
+  <si>
+    <t>7.30.3</t>
+  </si>
+  <si>
+    <t>7.30.4</t>
+  </si>
+  <si>
+    <t>7.30.5</t>
+  </si>
+  <si>
+    <t>7.30.6</t>
+  </si>
+  <si>
+    <t>7.30.7</t>
+  </si>
+  <si>
+    <t>7.30.8</t>
+  </si>
+  <si>
+    <t>7.30.9</t>
+  </si>
+  <si>
+    <t>7.30.10</t>
+  </si>
+  <si>
+    <t>7.30.11</t>
+  </si>
+  <si>
+    <t>7.30.12</t>
+  </si>
+  <si>
+    <t>7.30.13</t>
+  </si>
+  <si>
+    <t>7.30.14</t>
+  </si>
+  <si>
+    <t>7.30.15</t>
+  </si>
+  <si>
+    <t>7.30.16</t>
+  </si>
+  <si>
+    <t>7.30.17</t>
+  </si>
+  <si>
+    <t>7.30.18</t>
+  </si>
+  <si>
+    <t>7.30.19</t>
+  </si>
+  <si>
+    <t>7.30.20</t>
+  </si>
+  <si>
+    <t>7.30.21</t>
+  </si>
+  <si>
+    <t>7.30.22</t>
+  </si>
+  <si>
+    <t>7.31.1</t>
+  </si>
+  <si>
+    <t>7.31.2</t>
+  </si>
+  <si>
+    <t>7.32</t>
+  </si>
+  <si>
+    <t>7.53.1</t>
+  </si>
+  <si>
+    <t>7.53.2</t>
+  </si>
+  <si>
+    <t>7.53.3</t>
+  </si>
+  <si>
+    <t>7.53.4</t>
+  </si>
+  <si>
+    <t>7.54.1</t>
+  </si>
+  <si>
+    <t>7.54.2</t>
+  </si>
+  <si>
+    <t>7.54.3</t>
+  </si>
+  <si>
+    <t>7.54.4</t>
+  </si>
+  <si>
+    <t>7.55.1</t>
+  </si>
+  <si>
+    <t>7.55.2</t>
+  </si>
+  <si>
+    <t>7.55.3</t>
+  </si>
+  <si>
+    <t>7.55.4</t>
+  </si>
+  <si>
+    <t>7.57</t>
+  </si>
+  <si>
+    <t>7.58</t>
+  </si>
+  <si>
+    <t>7.61</t>
+  </si>
+  <si>
+    <t>7.61.1</t>
+  </si>
+  <si>
+    <t>7.61.2</t>
+  </si>
+  <si>
+    <t>7.62</t>
+  </si>
+  <si>
+    <t>7.74</t>
+  </si>
+  <si>
+    <t>7.74.1</t>
+  </si>
+  <si>
+    <t>7.75</t>
+  </si>
+  <si>
+    <t>7.76</t>
+  </si>
+  <si>
+    <t>7.76.1</t>
+  </si>
+  <si>
+    <t>7.77</t>
+  </si>
+  <si>
+    <t>7.77.1</t>
+  </si>
+  <si>
+    <t>7.78</t>
+  </si>
+  <si>
+    <t>8.7.1</t>
+  </si>
+  <si>
+    <t>8.7.2</t>
+  </si>
+  <si>
+    <t>8.13.1</t>
+  </si>
+  <si>
+    <t>8.17.1</t>
+  </si>
+  <si>
+    <t>10.1</t>
+  </si>
+  <si>
+    <t>10.6</t>
+  </si>
+  <si>
+    <t>12.1.1</t>
+  </si>
+  <si>
+    <t>12.1.2</t>
+  </si>
+  <si>
+    <t>12.1.3</t>
+  </si>
+  <si>
+    <t>12.2</t>
+  </si>
+  <si>
+    <t>12.2.1</t>
+  </si>
+  <si>
+    <t>12.6</t>
+  </si>
+  <si>
+    <t>12.6.1</t>
+  </si>
+  <si>
+    <t>Value chain mapping</t>
+  </si>
+  <si>
+    <t>Priority Locations</t>
+  </si>
+  <si>
+    <t>Risk Disclosure</t>
+  </si>
+  <si>
+    <t>Incentives</t>
+  </si>
+  <si>
+    <t>Environmental Policies</t>
+  </si>
+  <si>
+    <t>Scenario Analysis</t>
+  </si>
+  <si>
+    <t>Transition Plans</t>
+  </si>
+  <si>
+    <t>Value chain engagement</t>
+  </si>
+  <si>
+    <t>Emissions Methodology and Exclusions</t>
+  </si>
+  <si>
+    <t>Emissions Breakdown</t>
+  </si>
+  <si>
+    <t>Energy-Related Activities</t>
+  </si>
+  <si>
+    <t>Targets</t>
+  </si>
+  <si>
+    <t>Emissions Reduction Initiatives</t>
+  </si>
+  <si>
+    <t>Low-carbon products and services</t>
+  </si>
+  <si>
+    <t>Emissions</t>
+  </si>
+  <si>
+    <t>Ecosystem restoration projects</t>
+  </si>
+  <si>
+    <t>Activities</t>
+  </si>
+  <si>
+    <t>Metrics for durable goods and durable components</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metrics for end-of-life management </t>
+  </si>
+  <si>
+    <t>Environmental impact of portoflio and emissions breakdown (FS only)</t>
+  </si>
+  <si>
+    <t>Environmental impact of portfolio and emissions breakdown (FS only)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Environmentally sustainable products/services (FS only)  </t>
+  </si>
+  <si>
+    <t>KMWE</t>
+  </si>
+  <si>
+    <t>data avaliablity, missing weight: product type maretial type</t>
+  </si>
+  <si>
+    <t>print to build</t>
+  </si>
+  <si>
+    <t>role, regulations, product complaince, started with calculation of Scope 1, 2, and comminting to reduction by 2030</t>
+  </si>
+  <si>
+    <t>spend based is used</t>
+  </si>
+  <si>
+    <t>reduction 25% by scope 1, 2, 3 scope 2 malaysia is not grren</t>
+  </si>
+  <si>
+    <t>99% upstream scope 3: 70% purchased goods and services, waste, transportation</t>
+  </si>
+  <si>
+    <t>waste collection (no downstream information), packaging sustanaible</t>
+  </si>
+  <si>
+    <t>material data is getting from ai agent: nitish----&gt; path to activity-based calculation</t>
+  </si>
+  <si>
+    <t>30k-40k component parts</t>
+  </si>
+  <si>
+    <t>assembly part has no information on material types --- still working on</t>
+  </si>
+  <si>
+    <t>asml does not have the material type data</t>
+  </si>
+  <si>
+    <t>multi-tiered suppliers: information is deep layer</t>
+  </si>
+  <si>
+    <t>communciation between department comes before them</t>
+  </si>
+  <si>
+    <t>company emission factor- pressure from customers side</t>
+  </si>
+  <si>
+    <t>data quality== auditable</t>
+  </si>
+  <si>
+    <t>metals, ceramics, electronics, waste</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3d printing- reuse program no time to look at it : </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>initiative to change the design</t>
+    </r>
+  </si>
+  <si>
+    <t>focus on raw material</t>
+  </si>
+  <si>
+    <t>initiative of brainport development: data sharing, standardizing</t>
+  </si>
+  <si>
+    <t>focus on reduction now // and number</t>
+  </si>
+  <si>
+    <r>
+      <t>information gap-training</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  SUPPLIER TRAINING</t>
+    </r>
+  </si>
+  <si>
+    <t>green metals, reuse program, 3d printing</t>
+  </si>
+  <si>
+    <t>how to get information from suppliers</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1969,8 +3059,13 @@
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Roboto Light"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1983,8 +3078,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor theme="0" tint="-0.14999847407452621"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1992,11 +3093,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2018,11 +3143,31 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2033,6 +3178,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4320,11 +5469,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91855FF1-696F-485F-A9BD-8F77C0EFFEA1}">
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="67.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="96.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -4413,19 +5562,137 @@
         <v>438</v>
       </c>
     </row>
-    <row r="17" spans="2:2">
+    <row r="17" spans="1:2">
       <c r="B17" s="1" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="1:2">
       <c r="B18" t="s">
         <v>440</v>
       </c>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="1:2">
       <c r="B19" t="s">
         <v>441</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B20" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="B21" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="B22" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="B23" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="B24" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="B25" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="B26" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="B27" t="s">
+        <v>761</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="B28" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="B29" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="B30" t="s">
+        <v>764</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="B31" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="B32" t="s">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="33" spans="2:2">
+      <c r="B33" t="s">
+        <v>770</v>
+      </c>
+    </row>
+    <row r="34" spans="2:2">
+      <c r="B34" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="35" spans="2:2">
+      <c r="B35" t="s">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="36" spans="2:2">
+      <c r="B36" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="37" spans="2:2">
+      <c r="B37" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="38" spans="2:2">
+      <c r="B38" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="39" spans="2:2">
+      <c r="B39" s="1" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="40" spans="2:2">
+      <c r="B40" t="s">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="41" spans="2:2">
+      <c r="B41" s="1" t="s">
+        <v>775</v>
+      </c>
+    </row>
+    <row r="42" spans="2:2">
+      <c r="B42" t="s">
+        <v>776</v>
       </c>
     </row>
   </sheetData>
@@ -4435,9 +5702,2272 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60F9ECC2-9BD1-4D2D-8D1A-874AC48E7444}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="139.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="B1" t="s">
+        <v>443</v>
+      </c>
+      <c r="C1">
+        <v>2010</v>
+      </c>
+      <c r="D1">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B2" t="s">
+        <v>450</v>
+      </c>
+      <c r="C2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D2" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D3" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D4" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" t="s">
+        <v>451</v>
+      </c>
+      <c r="C6" t="s">
+        <v>445</v>
+      </c>
+      <c r="D6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>463</v>
+      </c>
+      <c r="B7" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" t="s">
+        <v>446</v>
+      </c>
+      <c r="D7" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C8" t="s">
+        <v>456</v>
+      </c>
+      <c r="D8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C9" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="C10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{92F8DC93-5681-4A25-B43A-D92D3E8CAABF}">
+  <dimension ref="A1:E153"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="56.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="B1" t="s">
+        <v>617</v>
+      </c>
+      <c r="C1" t="s">
+        <v>618</v>
+      </c>
+      <c r="D1">
+        <v>2024</v>
+      </c>
+      <c r="E1">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" ht="45">
+      <c r="A2" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="C2" s="11">
+        <v>1.24</v>
+      </c>
+      <c r="D2" s="11">
+        <v>1.24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="45">
+      <c r="A3" s="10" t="s">
+        <v>731</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45">
+      <c r="A4" s="9" t="s">
+        <v>731</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>469</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="45">
+      <c r="A5" s="10" t="s">
+        <v>732</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="C5" s="12">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="D5" s="12">
+        <v>2.2999999999999998</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="60">
+      <c r="A6" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="C6" s="11">
+        <v>3.1</v>
+      </c>
+      <c r="D6" s="11">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="60">
+      <c r="A7" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="45">
+      <c r="A8" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>473</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>622</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="60">
+      <c r="A9" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="C9" s="12">
+        <v>3.2</v>
+      </c>
+      <c r="D9" s="12">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="45">
+      <c r="A10" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="C10" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="D10" s="11">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="45">
+      <c r="A11" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>476</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>623</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="60">
+      <c r="A12" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>477</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>624</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="45">
+      <c r="A13" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>478</v>
+      </c>
+      <c r="C13" s="12">
+        <v>3.5</v>
+      </c>
+      <c r="D13" s="12">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="45">
+      <c r="A14" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>479</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>625</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="45">
+      <c r="A15" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>626</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="45">
+      <c r="A16" s="9" t="s">
+        <v>733</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>627</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="45">
+      <c r="A17" s="10" t="s">
+        <v>733</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="C17" s="12" t="s">
+        <v>628</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="45">
+      <c r="A18" s="9" t="s">
+        <v>734</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>483</v>
+      </c>
+      <c r="C18" s="11">
+        <v>4.5</v>
+      </c>
+      <c r="D18" s="11">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="45">
+      <c r="A19" s="10" t="s">
+        <v>734</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="C19" s="12" t="s">
+        <v>629</v>
+      </c>
+      <c r="D19" s="12" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="45">
+      <c r="A20" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>485</v>
+      </c>
+      <c r="C20" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D20" s="11">
+        <v>4.5999999999999996</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="45">
+      <c r="A21" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="C21" s="12" t="s">
+        <v>630</v>
+      </c>
+      <c r="D21" s="12" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="45">
+      <c r="A22" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>487</v>
+      </c>
+      <c r="C22" s="11">
+        <v>4.7</v>
+      </c>
+      <c r="D22" s="11">
+        <v>4.7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="45">
+      <c r="A23" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="C23" s="12" t="s">
+        <v>631</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="45">
+      <c r="A24" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>489</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>632</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" ht="45">
+      <c r="A25" s="10" t="s">
+        <v>735</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="C25" s="12">
+        <v>4.8</v>
+      </c>
+      <c r="D25" s="12">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="45">
+      <c r="A26" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>491</v>
+      </c>
+      <c r="C26" s="11" t="s">
+        <v>633</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="30">
+      <c r="A27" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="C27" s="12">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D27" s="12">
+        <v>5.0999999999999996</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="30">
+      <c r="A28" s="9" t="s">
+        <v>736</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>493</v>
+      </c>
+      <c r="C28" s="11" t="s">
+        <v>634</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="30">
+      <c r="A29" s="10" t="s">
+        <v>736</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="C29" s="12" t="s">
+        <v>635</v>
+      </c>
+      <c r="D29" s="12" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="30">
+      <c r="A30" s="9" t="s">
+        <v>737</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>495</v>
+      </c>
+      <c r="C30" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="D30" s="11">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" ht="60">
+      <c r="A31" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="C31" s="12" t="s">
+        <v>636</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" ht="60">
+      <c r="A32" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>497</v>
+      </c>
+      <c r="C32" s="11" t="s">
+        <v>637</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="60">
+      <c r="A33" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="C33" s="12" t="s">
+        <v>638</v>
+      </c>
+      <c r="D33" s="12" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="60">
+      <c r="A34" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>499</v>
+      </c>
+      <c r="C34" s="11" t="s">
+        <v>639</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="60">
+      <c r="A35" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>500</v>
+      </c>
+      <c r="C35" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="D35" s="12" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="60">
+      <c r="A36" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>501</v>
+      </c>
+      <c r="C36" s="11" t="s">
+        <v>641</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="60">
+      <c r="A37" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="60">
+      <c r="A38" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>503</v>
+      </c>
+      <c r="C38" s="11" t="s">
+        <v>643</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="60">
+      <c r="A39" s="10" t="s">
+        <v>738</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>644</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="60">
+      <c r="A40" s="9" t="s">
+        <v>738</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>505</v>
+      </c>
+      <c r="C40" s="11" t="s">
+        <v>645</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" ht="105">
+      <c r="A41" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="C41" s="12">
+        <v>7.1</v>
+      </c>
+      <c r="D41" s="12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" ht="105">
+      <c r="A42" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>507</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>646</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="105">
+      <c r="A43" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="C43" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" ht="105">
+      <c r="A44" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>509</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>648</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" ht="105">
+      <c r="A45" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>510</v>
+      </c>
+      <c r="C45" s="12">
+        <v>7.2</v>
+      </c>
+      <c r="D45" s="12">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="105">
+      <c r="A46" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>511</v>
+      </c>
+      <c r="C46" s="11">
+        <v>7.3</v>
+      </c>
+      <c r="D46" s="11">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" ht="105">
+      <c r="A47" s="10" t="s">
+        <v>739</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>512</v>
+      </c>
+      <c r="C47" s="12">
+        <v>7.4</v>
+      </c>
+      <c r="D47" s="12">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" ht="105">
+      <c r="A48" s="9" t="s">
+        <v>739</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>513</v>
+      </c>
+      <c r="C48" s="11" t="s">
+        <v>649</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="60">
+      <c r="A49" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="C49" s="12">
+        <v>7.15</v>
+      </c>
+      <c r="D49" s="12">
+        <v>7.15</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="60">
+      <c r="A50" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>515</v>
+      </c>
+      <c r="C50" s="11" t="s">
+        <v>650</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" ht="60">
+      <c r="A51" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B51" s="10" t="s">
+        <v>516</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" ht="60">
+      <c r="A52" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="C52" s="11" t="s">
+        <v>652</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" ht="60">
+      <c r="A53" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B53" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>653</v>
+      </c>
+      <c r="D53" s="12" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" ht="60">
+      <c r="A54" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>519</v>
+      </c>
+      <c r="C54" s="11">
+        <v>7.17</v>
+      </c>
+      <c r="D54" s="11">
+        <v>7.17</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" ht="60">
+      <c r="A55" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B55" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="C55" s="12" t="s">
+        <v>654</v>
+      </c>
+      <c r="D55" s="12" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="60">
+      <c r="A56" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>520</v>
+      </c>
+      <c r="C56" s="11" t="s">
+        <v>655</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" ht="60">
+      <c r="A57" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="C57" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="D57" s="12" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" ht="60">
+      <c r="A58" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>522</v>
+      </c>
+      <c r="C58" s="11">
+        <v>7.18</v>
+      </c>
+      <c r="D58" s="11">
+        <v>7.18</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" ht="60">
+      <c r="A59" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>657</v>
+      </c>
+      <c r="D59" s="12" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" ht="60">
+      <c r="A60" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>524</v>
+      </c>
+      <c r="C60" s="11" t="s">
+        <v>658</v>
+      </c>
+      <c r="D60" s="11" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" ht="60">
+      <c r="A61" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="C61" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="D61" s="12" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" ht="60">
+      <c r="A62" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>526</v>
+      </c>
+      <c r="C62" s="11">
+        <v>7.19</v>
+      </c>
+      <c r="D62" s="11">
+        <v>7.19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" ht="60">
+      <c r="A63" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>527</v>
+      </c>
+      <c r="C63" s="12" t="s">
+        <v>660</v>
+      </c>
+      <c r="D63" s="12" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="60">
+      <c r="A64" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>528</v>
+      </c>
+      <c r="C64" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="60">
+      <c r="A65" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="C65" s="12" t="s">
+        <v>662</v>
+      </c>
+      <c r="D65" s="12" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="60">
+      <c r="A66" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>530</v>
+      </c>
+      <c r="C66" s="11" t="s">
+        <v>663</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="60">
+      <c r="A67" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="C67" s="12">
+        <v>7.21</v>
+      </c>
+      <c r="D67" s="12">
+        <v>7.21</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="60">
+      <c r="A68" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>532</v>
+      </c>
+      <c r="C68" s="11">
+        <v>7.22</v>
+      </c>
+      <c r="D68" s="11">
+        <v>7.22</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="60">
+      <c r="A69" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B69" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="C69" s="12">
+        <v>7.23</v>
+      </c>
+      <c r="D69" s="12">
+        <v>7.23</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="60">
+      <c r="A70" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>534</v>
+      </c>
+      <c r="C70" s="11" t="s">
+        <v>664</v>
+      </c>
+      <c r="D70" s="11" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="60">
+      <c r="A71" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B71" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="C71" s="12">
+        <v>7.24</v>
+      </c>
+      <c r="D71" s="12">
+        <v>7.24</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="60">
+      <c r="A72" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>536</v>
+      </c>
+      <c r="C72" s="11">
+        <v>7.25</v>
+      </c>
+      <c r="D72" s="11">
+        <v>7.25</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="60">
+      <c r="A73" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B73" s="10" t="s">
+        <v>537</v>
+      </c>
+      <c r="C73" s="12" t="s">
+        <v>665</v>
+      </c>
+      <c r="D73" s="12" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="60">
+      <c r="A74" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>538</v>
+      </c>
+      <c r="C74" s="11">
+        <v>7.26</v>
+      </c>
+      <c r="D74" s="11">
+        <v>7.26</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="60">
+      <c r="A75" s="10" t="s">
+        <v>740</v>
+      </c>
+      <c r="B75" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="C75" s="12">
+        <v>7.27</v>
+      </c>
+      <c r="D75" s="12">
+        <v>7.27</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="60">
+      <c r="A76" s="9" t="s">
+        <v>740</v>
+      </c>
+      <c r="B76" s="9" t="s">
+        <v>540</v>
+      </c>
+      <c r="C76" s="11">
+        <v>7.28</v>
+      </c>
+      <c r="D76" s="11">
+        <v>7.28</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="60">
+      <c r="A77" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B77" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="C77" s="12">
+        <v>7.29</v>
+      </c>
+      <c r="D77" s="12">
+        <v>7.29</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="60">
+      <c r="A78" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>542</v>
+      </c>
+      <c r="C78" s="11" t="s">
+        <v>666</v>
+      </c>
+      <c r="D78" s="11" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="60">
+      <c r="A79" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B79" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="D79" s="12" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="60">
+      <c r="A80" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>544</v>
+      </c>
+      <c r="C80" s="11" t="s">
+        <v>668</v>
+      </c>
+      <c r="D80" s="11" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="60">
+      <c r="A81" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B81" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="C81" s="12" t="s">
+        <v>669</v>
+      </c>
+      <c r="D81" s="12" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="60">
+      <c r="A82" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B82" s="9" t="s">
+        <v>546</v>
+      </c>
+      <c r="C82" s="11" t="s">
+        <v>670</v>
+      </c>
+      <c r="D82" s="11" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="60">
+      <c r="A83" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B83" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="C83" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="D83" s="12" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="60">
+      <c r="A84" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B84" s="9" t="s">
+        <v>548</v>
+      </c>
+      <c r="C84" s="11" t="s">
+        <v>672</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="60">
+      <c r="A85" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B85" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="C85" s="12" t="s">
+        <v>673</v>
+      </c>
+      <c r="D85" s="12" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="60">
+      <c r="A86" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B86" s="9" t="s">
+        <v>550</v>
+      </c>
+      <c r="C86" s="11" t="s">
+        <v>674</v>
+      </c>
+      <c r="D86" s="11" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="60">
+      <c r="A87" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B87" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="C87" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="60">
+      <c r="A88" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B88" s="9" t="s">
+        <v>552</v>
+      </c>
+      <c r="C88" s="11" t="s">
+        <v>676</v>
+      </c>
+      <c r="D88" s="11" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="60">
+      <c r="A89" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B89" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>677</v>
+      </c>
+      <c r="D89" s="12" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="60">
+      <c r="A90" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B90" s="9" t="s">
+        <v>554</v>
+      </c>
+      <c r="C90" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="D90" s="11" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="60">
+      <c r="A91" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B91" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="C91" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="D91" s="12" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="60">
+      <c r="A92" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B92" s="9" t="s">
+        <v>556</v>
+      </c>
+      <c r="C92" s="11" t="s">
+        <v>680</v>
+      </c>
+      <c r="D92" s="11" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="60">
+      <c r="A93" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B93" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="C93" s="12" t="s">
+        <v>681</v>
+      </c>
+      <c r="D93" s="12" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="60">
+      <c r="A94" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B94" s="9" t="s">
+        <v>558</v>
+      </c>
+      <c r="C94" s="11" t="s">
+        <v>682</v>
+      </c>
+      <c r="D94" s="11" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="60">
+      <c r="A95" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B95" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="C95" s="12" t="s">
+        <v>683</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="60">
+      <c r="A96" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B96" s="9" t="s">
+        <v>560</v>
+      </c>
+      <c r="C96" s="11" t="s">
+        <v>684</v>
+      </c>
+      <c r="D96" s="11" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="60">
+      <c r="A97" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B97" s="10" t="s">
+        <v>561</v>
+      </c>
+      <c r="C97" s="12" t="s">
+        <v>685</v>
+      </c>
+      <c r="D97" s="12" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="60">
+      <c r="A98" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B98" s="9" t="s">
+        <v>562</v>
+      </c>
+      <c r="C98" s="11" t="s">
+        <v>686</v>
+      </c>
+      <c r="D98" s="11" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="60">
+      <c r="A99" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B99" s="10" t="s">
+        <v>563</v>
+      </c>
+      <c r="C99" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="D99" s="12" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="60">
+      <c r="A100" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B100" s="9" t="s">
+        <v>564</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="D100" s="11" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="60">
+      <c r="A101" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B101" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="C101" s="12">
+        <v>7.31</v>
+      </c>
+      <c r="D101" s="12">
+        <v>7.31</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="60">
+      <c r="A102" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>566</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>689</v>
+      </c>
+      <c r="D102" s="11" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="60">
+      <c r="A103" s="10" t="s">
+        <v>741</v>
+      </c>
+      <c r="B103" s="10" t="s">
+        <v>567</v>
+      </c>
+      <c r="C103" s="12" t="s">
+        <v>690</v>
+      </c>
+      <c r="D103" s="12" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="60">
+      <c r="A104" s="9" t="s">
+        <v>741</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>568</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>691</v>
+      </c>
+      <c r="D104" s="11" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="30">
+      <c r="A105" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B105" s="10" t="s">
+        <v>569</v>
+      </c>
+      <c r="C105" s="12">
+        <v>7.53</v>
+      </c>
+      <c r="D105" s="12">
+        <v>7.53</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="30">
+      <c r="A106" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B106" s="9" t="s">
+        <v>570</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>692</v>
+      </c>
+      <c r="D106" s="11" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="30">
+      <c r="A107" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B107" s="10" t="s">
+        <v>571</v>
+      </c>
+      <c r="C107" s="12" t="s">
+        <v>693</v>
+      </c>
+      <c r="D107" s="12" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="45">
+      <c r="A108" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B108" s="9" t="s">
+        <v>572</v>
+      </c>
+      <c r="C108" s="11" t="s">
+        <v>694</v>
+      </c>
+      <c r="D108" s="11" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="30">
+      <c r="A109" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B109" s="10" t="s">
+        <v>573</v>
+      </c>
+      <c r="C109" s="12" t="s">
+        <v>695</v>
+      </c>
+      <c r="D109" s="12" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="30">
+      <c r="A110" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B110" s="9" t="s">
+        <v>574</v>
+      </c>
+      <c r="C110" s="11">
+        <v>7.54</v>
+      </c>
+      <c r="D110" s="11">
+        <v>7.54</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="30">
+      <c r="A111" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B111" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="C111" s="12" t="s">
+        <v>696</v>
+      </c>
+      <c r="D111" s="12" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" ht="30">
+      <c r="A112" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B112" s="9" t="s">
+        <v>576</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>697</v>
+      </c>
+      <c r="D112" s="11" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4">
+      <c r="A113" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B113" s="10" t="s">
+        <v>577</v>
+      </c>
+      <c r="C113" s="12" t="s">
+        <v>698</v>
+      </c>
+      <c r="D113" s="12" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" ht="90">
+      <c r="A114" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B114" s="9" t="s">
+        <v>578</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>699</v>
+      </c>
+      <c r="D114" s="11" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" ht="90">
+      <c r="A115" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B115" s="10" t="s">
+        <v>579</v>
+      </c>
+      <c r="C115" s="12">
+        <v>7.55</v>
+      </c>
+      <c r="D115" s="12">
+        <v>7.55</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" ht="90">
+      <c r="A116" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B116" s="9" t="s">
+        <v>580</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>700</v>
+      </c>
+      <c r="D116" s="11" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" ht="90">
+      <c r="A117" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B117" s="10" t="s">
+        <v>581</v>
+      </c>
+      <c r="C117" s="12" t="s">
+        <v>701</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" ht="90">
+      <c r="A118" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B118" s="9" t="s">
+        <v>582</v>
+      </c>
+      <c r="C118" s="11" t="s">
+        <v>702</v>
+      </c>
+      <c r="D118" s="11" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" ht="90">
+      <c r="A119" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B119" s="10" t="s">
+        <v>583</v>
+      </c>
+      <c r="C119" s="12" t="s">
+        <v>703</v>
+      </c>
+      <c r="D119" s="12" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" ht="90">
+      <c r="A120" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B120" s="9" t="s">
+        <v>584</v>
+      </c>
+      <c r="C120" s="11">
+        <v>7.56</v>
+      </c>
+      <c r="D120" s="11">
+        <v>7.56</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" ht="90">
+      <c r="A121" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B121" s="10" t="s">
+        <v>585</v>
+      </c>
+      <c r="C121" s="12" t="s">
+        <v>704</v>
+      </c>
+      <c r="D121" s="12" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" ht="90">
+      <c r="A122" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B122" s="9" t="s">
+        <v>585</v>
+      </c>
+      <c r="C122" s="11" t="s">
+        <v>705</v>
+      </c>
+      <c r="D122" s="11" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" ht="90">
+      <c r="A123" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B123" s="10" t="s">
+        <v>586</v>
+      </c>
+      <c r="C123" s="12" t="s">
+        <v>706</v>
+      </c>
+      <c r="D123" s="12" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" ht="90">
+      <c r="A124" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B124" s="9" t="s">
+        <v>587</v>
+      </c>
+      <c r="C124" s="11" t="s">
+        <v>707</v>
+      </c>
+      <c r="D124" s="11" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" ht="90">
+      <c r="A125" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="B125" s="10" t="s">
+        <v>588</v>
+      </c>
+      <c r="C125" s="12" t="s">
+        <v>708</v>
+      </c>
+      <c r="D125" s="12" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" ht="90">
+      <c r="A126" s="9" t="s">
+        <v>743</v>
+      </c>
+      <c r="B126" s="9" t="s">
+        <v>589</v>
+      </c>
+      <c r="C126" s="11" t="s">
+        <v>709</v>
+      </c>
+      <c r="D126" s="11" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" ht="75">
+      <c r="A127" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="B127" s="10" t="s">
+        <v>590</v>
+      </c>
+      <c r="C127" s="12" t="s">
+        <v>710</v>
+      </c>
+      <c r="D127" s="12" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" ht="75">
+      <c r="A128" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B128" s="9" t="s">
+        <v>591</v>
+      </c>
+      <c r="C128" s="11" t="s">
+        <v>711</v>
+      </c>
+      <c r="D128" s="11" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" ht="75">
+      <c r="A129" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="B129" s="10" t="s">
+        <v>592</v>
+      </c>
+      <c r="C129" s="12" t="s">
+        <v>712</v>
+      </c>
+      <c r="D129" s="12" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" ht="75">
+      <c r="A130" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>593</v>
+      </c>
+      <c r="C130" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="D130" s="11" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" ht="75">
+      <c r="A131" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>594</v>
+      </c>
+      <c r="C131" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="D131" s="12" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" ht="75">
+      <c r="A132" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>595</v>
+      </c>
+      <c r="C132" s="11" t="s">
+        <v>715</v>
+      </c>
+      <c r="D132" s="11" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" ht="75">
+      <c r="A133" s="10" t="s">
+        <v>744</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>596</v>
+      </c>
+      <c r="C133" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="D133" s="12" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" ht="75">
+      <c r="A134" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>597</v>
+      </c>
+      <c r="C134" s="11" t="s">
+        <v>717</v>
+      </c>
+      <c r="D134" s="11" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" ht="60">
+      <c r="A135" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>598</v>
+      </c>
+      <c r="C135" s="12">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="D135" s="12">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" ht="30">
+      <c r="A136" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>599</v>
+      </c>
+      <c r="C136" s="11" t="s">
+        <v>718</v>
+      </c>
+      <c r="D136" s="11" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" ht="60">
+      <c r="A137" s="10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>600</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>719</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" ht="60">
+      <c r="A138" s="9" t="s">
+        <v>745</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>601</v>
+      </c>
+      <c r="C138" s="11">
+        <v>8.1300000000000008</v>
+      </c>
+      <c r="D138" s="11">
+        <v>8.1300000000000008</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" ht="60">
+      <c r="A139" s="10" t="s">
+        <v>745</v>
+      </c>
+      <c r="B139" s="10" t="s">
+        <v>602</v>
+      </c>
+      <c r="C139" s="12" t="s">
+        <v>720</v>
+      </c>
+      <c r="D139" s="12" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" ht="75">
+      <c r="A140" s="9" t="s">
+        <v>746</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>603</v>
+      </c>
+      <c r="C140" s="11">
+        <v>8.17</v>
+      </c>
+      <c r="D140" s="11">
+        <v>8.17</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" ht="75">
+      <c r="A141" s="10" t="s">
+        <v>746</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>604</v>
+      </c>
+      <c r="C141" s="12" t="s">
+        <v>721</v>
+      </c>
+      <c r="D141" s="12" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4">
+      <c r="A142" s="9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>605</v>
+      </c>
+      <c r="C142" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="D142" s="11" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" ht="30">
+      <c r="A143" s="10" t="s">
+        <v>747</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>606</v>
+      </c>
+      <c r="C143" s="12">
+        <v>10.199999999999999</v>
+      </c>
+      <c r="D143" s="12">
+        <v>10.199999999999999</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" ht="120">
+      <c r="A144" s="9" t="s">
+        <v>748</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>607</v>
+      </c>
+      <c r="C144" s="11">
+        <v>10.4</v>
+      </c>
+      <c r="D144" s="11">
+        <v>10.4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" ht="75">
+      <c r="A145" s="10" t="s">
+        <v>749</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>608</v>
+      </c>
+      <c r="C145" s="12" t="s">
+        <v>723</v>
+      </c>
+      <c r="D145" s="12" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" ht="165">
+      <c r="A146" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>609</v>
+      </c>
+      <c r="C146" s="11">
+        <v>12.1</v>
+      </c>
+      <c r="D146" s="11">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" ht="165">
+      <c r="A147" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>610</v>
+      </c>
+      <c r="C147" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="D147" s="12" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" ht="165">
+      <c r="A148" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>611</v>
+      </c>
+      <c r="C148" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="D148" s="11" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" ht="165">
+      <c r="A149" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>612</v>
+      </c>
+      <c r="C149" s="12" t="s">
+        <v>726</v>
+      </c>
+      <c r="D149" s="12" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" ht="165">
+      <c r="A150" s="9" t="s">
+        <v>751</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>613</v>
+      </c>
+      <c r="C150" s="11" t="s">
+        <v>727</v>
+      </c>
+      <c r="D150" s="11" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" ht="165">
+      <c r="A151" s="10" t="s">
+        <v>751</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>614</v>
+      </c>
+      <c r="C151" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="D151" s="12" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" ht="120">
+      <c r="A152" s="9" t="s">
+        <v>752</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>615</v>
+      </c>
+      <c r="C152" s="11" t="s">
+        <v>729</v>
+      </c>
+      <c r="D152" s="11" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" ht="120">
+      <c r="A153" s="10" t="s">
+        <v>752</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>616</v>
+      </c>
+      <c r="C153" s="12" t="s">
+        <v>730</v>
+      </c>
+      <c r="D153" s="12" t="s">
+        <v>730</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A2:D153">
+    <cfRule type="containsBlanks" dxfId="0" priority="1">
+      <formula>LEN(TRIM(A2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
